--- a/Descargas/PL MPSA Winner TK Hoses Apr 8th 2025.xlsx
+++ b/Descargas/PL MPSA Winner TK Hoses Apr 8th 2025.xlsx
@@ -7323,13 +7323,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C5D2B86-EA26-4B5E-98F0-2B6E2B67201F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78D6B12F-248F-4BFA-871F-ACFB76FCEEE3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0C35CF9-4DC5-4590-9972-B85FB48793E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01882525-463B-4460-B724-C8BBFAA5929C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFFB8210-F2A1-44E2-9F8D-DB3AA2F8D79E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6682F152-C4C2-4BDD-AF2D-B5C16AE25306}"/>
 </file>